--- a/Output/VO2maxQC/quality_differences.EasyTrial.xlsx
+++ b/Output/VO2maxQC/quality_differences.EasyTrial.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -432,10 +432,10 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>6.666666666666667</v>
+        <v>5.88235294117647</v>
       </c>
     </row>
     <row r="5">
@@ -448,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>93.33333333333333</v>
+        <v>94.11764705882352</v>
       </c>
     </row>
     <row r="6">
@@ -470,35 +470,35 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Iben</t>
+          <t>Clara og Iben</t>
         </is>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Malte</t>
+          <t>Iben</t>
         </is>
       </c>
       <c r="B8" t="b">
@@ -508,73 +508,73 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="E8">
-        <v>0.9615384615384616</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Malte</t>
+          <t>Iben</t>
         </is>
       </c>
       <c r="B9" t="b">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="E9">
-        <v>99.03846153846155</v>
+        <v>92.30769230769231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Malte og Iben</t>
+          <t>Malte</t>
         </is>
       </c>
       <c r="B10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>0.9615384615384616</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marie Louise</t>
+          <t>Malte</t>
         </is>
       </c>
       <c r="B11" t="b">
         <v>1</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>99.03846153846155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Malte og Iben</t>
         </is>
       </c>
       <c r="B12" t="b">
@@ -591,17 +591,69 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Marie Louise</t>
+        </is>
+      </c>
       <c r="B13" t="b">
         <v>1</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15">
+        <v>14.28571428571428</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+      <c r="E16">
+        <v>85.71428571428571</v>
       </c>
     </row>
   </sheetData>
